--- a/output/Data and Chart Outputs/spain_ree_exchanges_daily.xlsx
+++ b/output/Data and Chart Outputs/spain_ree_exchanges_daily.xlsx
@@ -155,7 +155,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Spain net imports from Morocco and Andorra (REE, negative = export) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Spain net imports from Morocco and Andorra (REE, negative = export) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -191,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -227,12 +228,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -696,7 +697,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-04 23:41 UTC; 2021-01-01 to 2026-09-22</t>
+          <t>2026-10-28 00:56 UTC; 2021-01-01 to 2026-10-15</t>
         </is>
       </c>
     </row>
@@ -711,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -742,7 +743,7 @@
         <v>55.47519999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>-38.4191</v>
+        <v>-38.41910000000001</v>
       </c>
     </row>
     <row r="3">
@@ -750,10 +751,10 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>-8.6976</v>
+        <v>-8.697599999999998</v>
       </c>
       <c r="C3" t="n">
-        <v>-28.394</v>
+        <v>-28.39399999999999</v>
       </c>
     </row>
     <row r="4">
@@ -761,10 +762,10 @@
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>36.6579</v>
+        <v>36.65789999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>-22.8928</v>
+        <v>-22.89279999999999</v>
       </c>
     </row>
     <row r="5">
@@ -772,7 +773,7 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>37.6149</v>
+        <v>37.61489999999999</v>
       </c>
       <c r="C5" t="n">
         <v>-12.1092</v>
@@ -783,7 +784,7 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>58.27</v>
+        <v>58.27000000000001</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -797,7 +798,7 @@
         <v>23.039</v>
       </c>
       <c r="C7" t="n">
-        <v>-5.126600000000001</v>
+        <v>-5.1266</v>
       </c>
     </row>
     <row r="8">
@@ -805,7 +806,7 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>-38.6349</v>
+        <v>-38.63490000000002</v>
       </c>
       <c r="C8" t="n">
         <v>-3.5506</v>
@@ -838,7 +839,7 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>59.0079</v>
+        <v>59.00790000000001</v>
       </c>
       <c r="C11" t="n">
         <v>-15.1944</v>
@@ -849,7 +850,7 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.998499999999999</v>
+        <v>-1.998499999999997</v>
       </c>
       <c r="C12" t="n">
         <v>-28.6321</v>
@@ -860,10 +861,10 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>48.5145</v>
+        <v>48.51450000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>-40.654</v>
+        <v>-40.65399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -871,7 +872,7 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>57.1192</v>
+        <v>57.11919999999999</v>
       </c>
       <c r="C14" t="n">
         <v>-38.4838</v>
@@ -896,7 +897,7 @@
         <v>22.0227</v>
       </c>
       <c r="C16" t="n">
-        <v>-31.125</v>
+        <v>-31.12499999999999</v>
       </c>
     </row>
     <row r="17">
@@ -918,7 +919,7 @@
         <v>-37.9871</v>
       </c>
       <c r="C18" t="n">
-        <v>-5.3542</v>
+        <v>-5.354200000000001</v>
       </c>
     </row>
     <row r="19">
@@ -926,7 +927,7 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>-205.0779</v>
+        <v>-205.0779000000001</v>
       </c>
       <c r="C19" t="n">
         <v>-16.5392</v>
@@ -995,7 +996,7 @@
         <v>-149.9671</v>
       </c>
       <c r="C25" t="n">
-        <v>-39.8803</v>
+        <v>-39.88030000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1006,7 +1007,7 @@
         <v>-131.6919</v>
       </c>
       <c r="C26" t="n">
-        <v>-42.4545</v>
+        <v>-42.45450000000002</v>
       </c>
     </row>
     <row r="27">
@@ -1017,7 +1018,7 @@
         <v>-187.1123</v>
       </c>
       <c r="C27" t="n">
-        <v>-21.2056</v>
+        <v>-21.20560000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1058,10 +1059,10 @@
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>-42.7007</v>
+        <v>-42.70069999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>-2.0795</v>
+        <v>-2.079499999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1072,7 +1073,7 @@
         <v>-174.7156</v>
       </c>
       <c r="C32" t="n">
-        <v>-19.2309</v>
+        <v>-19.23089999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1080,7 +1081,7 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>-376.7937</v>
+        <v>-376.7936999999999</v>
       </c>
       <c r="C33" t="n">
         <v>-19.9376</v>
@@ -1116,7 +1117,7 @@
         <v>-162.2858</v>
       </c>
       <c r="C36" t="n">
-        <v>-23.8338</v>
+        <v>-23.83379999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1127,7 +1128,7 @@
         <v>-106.1756</v>
       </c>
       <c r="C37" t="n">
-        <v>-34.648</v>
+        <v>-34.64800000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1135,10 +1136,10 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>-38.22070000000001</v>
+        <v>-38.22069999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-40.62280000000001</v>
+        <v>-40.62279999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1182,7 +1183,7 @@
         <v>-303.9685</v>
       </c>
       <c r="C42" t="n">
-        <v>-6.7133</v>
+        <v>-6.713299999999999</v>
       </c>
     </row>
     <row r="43">
@@ -1201,7 +1202,7 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>-308.7555</v>
+        <v>-308.7554999999999</v>
       </c>
       <c r="C44" t="n">
         <v>-18.9427</v>
@@ -1212,7 +1213,7 @@
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>-290.2765</v>
+        <v>-290.2764999999999</v>
       </c>
       <c r="C45" t="n">
         <v>-1.8505</v>
@@ -1223,7 +1224,7 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>-311.5397</v>
+        <v>-311.5397000000001</v>
       </c>
       <c r="C46" t="n">
         <v>-26.3144</v>
@@ -1237,7 +1238,7 @@
         <v>-270.7604</v>
       </c>
       <c r="C47" t="n">
-        <v>-9.4001</v>
+        <v>-9.400099999999998</v>
       </c>
     </row>
     <row r="48">
@@ -1270,7 +1271,7 @@
         <v>-90.2</v>
       </c>
       <c r="C50" t="n">
-        <v>-34.2618</v>
+        <v>-34.26179999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1322,7 +1323,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>-395.0249</v>
+        <v>-395.0248999999999</v>
       </c>
       <c r="C55" t="n">
         <v>-13.889</v>
@@ -1344,7 +1345,7 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>-448.6696</v>
+        <v>-448.6696000000001</v>
       </c>
       <c r="C57" t="n">
         <v>-17.9152</v>
@@ -1355,7 +1356,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>-339.6061</v>
+        <v>-339.6061000000001</v>
       </c>
       <c r="C58" t="n">
         <v>-16.6628</v>
@@ -1388,7 +1389,7 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>-360.2123</v>
+        <v>-360.2122999999999</v>
       </c>
       <c r="C61" t="n">
         <v>-24.3546</v>
@@ -1399,7 +1400,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>-202.5952</v>
+        <v>-202.5951999999999</v>
       </c>
       <c r="C62" t="n">
         <v>-38.6088</v>
@@ -1410,7 +1411,7 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>-318.777</v>
+        <v>-318.7769999999999</v>
       </c>
       <c r="C63" t="n">
         <v>-23.7255</v>
@@ -1454,7 +1455,7 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>-437.8107</v>
+        <v>-437.8106999999999</v>
       </c>
       <c r="C67" t="n">
         <v>-12.1498</v>
@@ -1465,7 +1466,7 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>-529.8416</v>
+        <v>-529.8416000000001</v>
       </c>
       <c r="C68" t="n">
         <v>-22.9108</v>
@@ -1480,6 +1481,17 @@
       </c>
       <c r="C69" t="n">
         <v>-24.7119</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>-507.441</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-25.07300000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2092"/>
+  <dimension ref="A1:F2115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1674,7 +1686,7 @@
         <v>44204</v>
       </c>
       <c r="B9" t="n">
-        <v>1285.6</v>
+        <v>1285.5</v>
       </c>
       <c r="C9" t="n">
         <v>2436.5</v>
@@ -1954,7 +1966,7 @@
         <v>44218</v>
       </c>
       <c r="B23" t="n">
-        <v>1196.8</v>
+        <v>1196.9</v>
       </c>
       <c r="C23" t="n">
         <v>2406.3</v>
@@ -2254,7 +2266,7 @@
         <v>44233</v>
       </c>
       <c r="B38" t="n">
-        <v>-1060</v>
+        <v>-1060.1</v>
       </c>
       <c r="C38" t="n">
         <v>77.3</v>
@@ -3114,7 +3126,7 @@
         <v>44276</v>
       </c>
       <c r="B81" t="n">
-        <v>2338.1</v>
+        <v>2338.2</v>
       </c>
       <c r="C81" t="n">
         <v>3121.6</v>
@@ -3854,7 +3866,7 @@
         <v>44313</v>
       </c>
       <c r="B118" t="n">
-        <v>3279.6</v>
+        <v>3279.7</v>
       </c>
       <c r="C118" t="n">
         <v>3727.9</v>
@@ -5514,7 +5526,7 @@
         <v>44396</v>
       </c>
       <c r="B201" t="n">
-        <v>2072.2</v>
+        <v>2072.1</v>
       </c>
       <c r="C201" t="n">
         <v>2161.1</v>
@@ -7114,7 +7126,7 @@
         <v>44476</v>
       </c>
       <c r="B281" t="n">
-        <v>-216.5</v>
+        <v>-216.6</v>
       </c>
       <c r="C281" t="n">
         <v>262.7</v>
@@ -7794,7 +7806,7 @@
         <v>44510</v>
       </c>
       <c r="B315" t="n">
-        <v>-3707</v>
+        <v>-3706.9</v>
       </c>
       <c r="C315" t="n">
         <v>-2882.1</v>
@@ -8434,7 +8446,7 @@
         <v>44542</v>
       </c>
       <c r="B347" t="n">
-        <v>3709.2</v>
+        <v>3709.1</v>
       </c>
       <c r="C347" t="n">
         <v>5027.3</v>
@@ -8454,7 +8466,7 @@
         <v>44543</v>
       </c>
       <c r="B348" t="n">
-        <v>844.4</v>
+        <v>844.3</v>
       </c>
       <c r="C348" t="n">
         <v>2156.9</v>
@@ -9754,7 +9766,7 @@
         <v>44608</v>
       </c>
       <c r="B413" t="n">
-        <v>-4056.6</v>
+        <v>-4056.5</v>
       </c>
       <c r="C413" t="n">
         <v>-2710.1</v>
@@ -10234,7 +10246,7 @@
         <v>44632</v>
       </c>
       <c r="B437" t="n">
-        <v>-1184.1</v>
+        <v>-1184.2</v>
       </c>
       <c r="C437" t="n">
         <v>88.2</v>
@@ -10654,7 +10666,7 @@
         <v>44653</v>
       </c>
       <c r="B458" t="n">
-        <v>-3581.8</v>
+        <v>-3581.9</v>
       </c>
       <c r="C458" t="n">
         <v>-2657.3</v>
@@ -10774,7 +10786,7 @@
         <v>44659</v>
       </c>
       <c r="B464" t="n">
-        <v>-2479.2</v>
+        <v>-2479.3</v>
       </c>
       <c r="C464" t="n">
         <v>-1501.9</v>
@@ -11094,7 +11106,7 @@
         <v>44675</v>
       </c>
       <c r="B480" t="n">
-        <v>-2922</v>
+        <v>-2921.9</v>
       </c>
       <c r="C480" t="n">
         <v>-2532.9</v>
@@ -11254,7 +11266,7 @@
         <v>44683</v>
       </c>
       <c r="B488" t="n">
-        <v>8870.799999999999</v>
+        <v>8870.700000000001</v>
       </c>
       <c r="C488" t="n">
         <v>9052.5</v>
@@ -11454,7 +11466,7 @@
         <v>44693</v>
       </c>
       <c r="B498" t="n">
-        <v>-7306.6</v>
+        <v>-7306.7</v>
       </c>
       <c r="C498" t="n">
         <v>-7221.1</v>
@@ -12734,7 +12746,7 @@
         <v>44757</v>
       </c>
       <c r="B562" t="n">
-        <v>-355.5</v>
+        <v>-355.6</v>
       </c>
       <c r="C562" t="n">
         <v>83.40000000000001</v>
@@ -12814,7 +12826,7 @@
         <v>44761</v>
       </c>
       <c r="B566" t="n">
-        <v>-3844.2</v>
+        <v>-3844.3</v>
       </c>
       <c r="C566" t="n">
         <v>-3385.3</v>
@@ -15054,7 +15066,7 @@
         <v>44873</v>
       </c>
       <c r="B678" t="n">
-        <v>-7322.2</v>
+        <v>-7322.1</v>
       </c>
       <c r="C678" t="n">
         <v>-6614.1</v>
@@ -15694,7 +15706,7 @@
         <v>44905</v>
       </c>
       <c r="B710" t="n">
-        <v>-1171.2</v>
+        <v>-1171.1</v>
       </c>
       <c r="C710" t="n">
         <v>191.5</v>
@@ -15854,7 +15866,7 @@
         <v>44913</v>
       </c>
       <c r="B718" t="n">
-        <v>-2477</v>
+        <v>-2477.1</v>
       </c>
       <c r="C718" t="n">
         <v>-1124.7</v>
@@ -15914,7 +15926,7 @@
         <v>44916</v>
       </c>
       <c r="B721" t="n">
-        <v>-8202.4</v>
+        <v>-8202.299999999999</v>
       </c>
       <c r="C721" t="n">
         <v>-6977.5</v>
@@ -16314,7 +16326,7 @@
         <v>44936</v>
       </c>
       <c r="B741" t="n">
-        <v>-5806.5</v>
+        <v>-5806.6</v>
       </c>
       <c r="C741" t="n">
         <v>-4494.4</v>
@@ -16554,7 +16566,7 @@
         <v>44948</v>
       </c>
       <c r="B753" t="n">
-        <v>-2249.8</v>
+        <v>-2249.9</v>
       </c>
       <c r="C753" t="n">
         <v>-785.5</v>
@@ -17154,7 +17166,7 @@
         <v>44978</v>
       </c>
       <c r="B783" t="n">
-        <v>-10101.6</v>
+        <v>-10101.7</v>
       </c>
       <c r="C783" t="n">
         <v>-9638.9</v>
@@ -18314,7 +18326,7 @@
         <v>45036</v>
       </c>
       <c r="B841" t="n">
-        <v>199.8</v>
+        <v>199.9</v>
       </c>
       <c r="C841" t="n">
         <v>801.9</v>
@@ -18474,7 +18486,7 @@
         <v>45044</v>
       </c>
       <c r="B849" t="n">
-        <v>-6955.2</v>
+        <v>-6955.1</v>
       </c>
       <c r="C849" t="n">
         <v>-6685.3</v>
@@ -20274,7 +20286,7 @@
         <v>45134</v>
       </c>
       <c r="B939" t="n">
-        <v>-5297.2</v>
+        <v>-5297.3</v>
       </c>
       <c r="C939" t="n">
         <v>-4727.1</v>
@@ -21134,7 +21146,7 @@
         <v>45177</v>
       </c>
       <c r="B982" t="n">
-        <v>-8510.200000000001</v>
+        <v>-8510.1</v>
       </c>
       <c r="C982" t="n">
         <v>-8201.1</v>
@@ -21454,7 +21466,7 @@
         <v>45193</v>
       </c>
       <c r="B998" t="n">
-        <v>-7393</v>
+        <v>-7393.1</v>
       </c>
       <c r="C998" t="n">
         <v>-7047.3</v>
@@ -21774,7 +21786,7 @@
         <v>45209</v>
       </c>
       <c r="B1014" t="n">
-        <v>1259.3</v>
+        <v>1259.2</v>
       </c>
       <c r="C1014" t="n">
         <v>2064.9</v>
@@ -21874,7 +21886,7 @@
         <v>45214</v>
       </c>
       <c r="B1019" t="n">
-        <v>-5009.9</v>
+        <v>-5009.8</v>
       </c>
       <c r="C1019" t="n">
         <v>-4652.7</v>
@@ -21934,7 +21946,7 @@
         <v>45217</v>
       </c>
       <c r="B1022" t="n">
-        <v>-17987.8</v>
+        <v>-17987.7</v>
       </c>
       <c r="C1022" t="n">
         <v>-17564.3</v>
@@ -22074,7 +22086,7 @@
         <v>45224</v>
       </c>
       <c r="B1029" t="n">
-        <v>2725.8</v>
+        <v>2725.7</v>
       </c>
       <c r="C1029" t="n">
         <v>3129.5</v>
@@ -22154,7 +22166,7 @@
         <v>45228</v>
       </c>
       <c r="B1033" t="n">
-        <v>-15148.8</v>
+        <v>-15148.7</v>
       </c>
       <c r="C1033" t="n">
         <v>-14549.9</v>
@@ -22214,7 +22226,7 @@
         <v>45231</v>
       </c>
       <c r="B1036" t="n">
-        <v>-18167.1</v>
+        <v>-18167</v>
       </c>
       <c r="C1036" t="n">
         <v>-17410.9</v>
@@ -22474,7 +22486,7 @@
         <v>45244</v>
       </c>
       <c r="B1049" t="n">
-        <v>-14534.5</v>
+        <v>-14534.6</v>
       </c>
       <c r="C1049" t="n">
         <v>-13861.7</v>
@@ -22534,7 +22546,7 @@
         <v>45247</v>
       </c>
       <c r="B1052" t="n">
-        <v>-8391.6</v>
+        <v>-8391.700000000001</v>
       </c>
       <c r="C1052" t="n">
         <v>-7575.7</v>
@@ -22554,7 +22566,7 @@
         <v>45248</v>
       </c>
       <c r="B1053" t="n">
-        <v>-6152.9</v>
+        <v>-6152.8</v>
       </c>
       <c r="C1053" t="n">
         <v>-5232.2</v>
@@ -22614,7 +22626,7 @@
         <v>45251</v>
       </c>
       <c r="B1056" t="n">
-        <v>-2779.8</v>
+        <v>-2779.7</v>
       </c>
       <c r="C1056" t="n">
         <v>-1757.2</v>
@@ -22634,7 +22646,7 @@
         <v>45252</v>
       </c>
       <c r="B1057" t="n">
-        <v>-6554.2</v>
+        <v>-6554.1</v>
       </c>
       <c r="C1057" t="n">
         <v>-5447.4</v>
@@ -22694,7 +22706,7 @@
         <v>45255</v>
       </c>
       <c r="B1060" t="n">
-        <v>-2745.5</v>
+        <v>-2745.4</v>
       </c>
       <c r="C1060" t="n">
         <v>-1783.5</v>
@@ -22774,7 +22786,7 @@
         <v>45259</v>
       </c>
       <c r="B1064" t="n">
-        <v>-6637.3</v>
+        <v>-6637.2</v>
       </c>
       <c r="C1064" t="n">
         <v>-5717.7</v>
@@ -22894,7 +22906,7 @@
         <v>45265</v>
       </c>
       <c r="B1070" t="n">
-        <v>-6809.8</v>
+        <v>-6809.9</v>
       </c>
       <c r="C1070" t="n">
         <v>-6108.7</v>
@@ -23014,7 +23026,7 @@
         <v>45271</v>
       </c>
       <c r="B1076" t="n">
-        <v>-13474.6</v>
+        <v>-13474.7</v>
       </c>
       <c r="C1076" t="n">
         <v>-12542.2</v>
@@ -23134,7 +23146,7 @@
         <v>45277</v>
       </c>
       <c r="B1082" t="n">
-        <v>3058.5</v>
+        <v>3058.4</v>
       </c>
       <c r="C1082" t="n">
         <v>4379.6</v>
@@ -23154,7 +23166,7 @@
         <v>45278</v>
       </c>
       <c r="B1083" t="n">
-        <v>3468.7</v>
+        <v>3468.8</v>
       </c>
       <c r="C1083" t="n">
         <v>4592.2</v>
@@ -23214,7 +23226,7 @@
         <v>45281</v>
       </c>
       <c r="B1086" t="n">
-        <v>-2839.9</v>
+        <v>-2840</v>
       </c>
       <c r="C1086" t="n">
         <v>-1576.2</v>
@@ -23334,7 +23346,7 @@
         <v>45287</v>
       </c>
       <c r="B1092" t="n">
-        <v>-6552.3</v>
+        <v>-6552.4</v>
       </c>
       <c r="C1092" t="n">
         <v>-5359.2</v>
@@ -23374,7 +23386,7 @@
         <v>45289</v>
       </c>
       <c r="B1094" t="n">
-        <v>-497.6</v>
+        <v>-497.7</v>
       </c>
       <c r="C1094" t="n">
         <v>751</v>
@@ -23394,7 +23406,7 @@
         <v>45290</v>
       </c>
       <c r="B1095" t="n">
-        <v>-1488.7</v>
+        <v>-1488.8</v>
       </c>
       <c r="C1095" t="n">
         <v>-122.3</v>
@@ -23434,7 +23446,7 @@
         <v>45292</v>
       </c>
       <c r="B1097" t="n">
-        <v>-5908.9</v>
+        <v>-5908.8</v>
       </c>
       <c r="C1097" t="n">
         <v>-4574.2</v>
@@ -23494,7 +23506,7 @@
         <v>45295</v>
       </c>
       <c r="B1100" t="n">
-        <v>-4010.6</v>
+        <v>-4010.5</v>
       </c>
       <c r="C1100" t="n">
         <v>-2725.9</v>
@@ -23534,7 +23546,7 @@
         <v>45297</v>
       </c>
       <c r="B1102" t="n">
-        <v>-1329.6</v>
+        <v>-1329.5</v>
       </c>
       <c r="C1102" t="n">
         <v>102</v>
@@ -23554,7 +23566,7 @@
         <v>45298</v>
       </c>
       <c r="B1103" t="n">
-        <v>1237.2</v>
+        <v>1237.3</v>
       </c>
       <c r="C1103" t="n">
         <v>2665.7</v>
@@ -23594,7 +23606,7 @@
         <v>45300</v>
       </c>
       <c r="B1105" t="n">
-        <v>-4619.1</v>
+        <v>-4619</v>
       </c>
       <c r="C1105" t="n">
         <v>-2967.4</v>
@@ -23634,7 +23646,7 @@
         <v>45302</v>
       </c>
       <c r="B1107" t="n">
-        <v>858.2</v>
+        <v>858.3</v>
       </c>
       <c r="C1107" t="n">
         <v>2450.1</v>
@@ -23654,7 +23666,7 @@
         <v>45303</v>
       </c>
       <c r="B1108" t="n">
-        <v>-102.1</v>
+        <v>-102.2</v>
       </c>
       <c r="C1108" t="n">
         <v>1307</v>
@@ -23674,7 +23686,7 @@
         <v>45304</v>
       </c>
       <c r="B1109" t="n">
-        <v>178.5</v>
+        <v>178.6</v>
       </c>
       <c r="C1109" t="n">
         <v>1689.6</v>
@@ -23694,7 +23706,7 @@
         <v>45305</v>
       </c>
       <c r="B1110" t="n">
-        <v>1675.1</v>
+        <v>1675.2</v>
       </c>
       <c r="C1110" t="n">
         <v>3061.4</v>
@@ -23754,7 +23766,7 @@
         <v>45308</v>
       </c>
       <c r="B1113" t="n">
-        <v>-10632.8</v>
+        <v>-10632.9</v>
       </c>
       <c r="C1113" t="n">
         <v>-9361.700000000001</v>
@@ -23934,7 +23946,7 @@
         <v>45317</v>
       </c>
       <c r="B1122" t="n">
-        <v>-1456.2</v>
+        <v>-1456.3</v>
       </c>
       <c r="C1122" t="n">
         <v>-327.7</v>
@@ -23954,7 +23966,7 @@
         <v>45318</v>
       </c>
       <c r="B1123" t="n">
-        <v>-1784.4</v>
+        <v>-1784.5</v>
       </c>
       <c r="C1123" t="n">
         <v>-519.5</v>
@@ -24034,7 +24046,7 @@
         <v>45322</v>
       </c>
       <c r="B1127" t="n">
-        <v>-3448.7</v>
+        <v>-3448.8</v>
       </c>
       <c r="C1127" t="n">
         <v>-2329.8</v>
@@ -24114,7 +24126,7 @@
         <v>45326</v>
       </c>
       <c r="B1131" t="n">
-        <v>-1064.6</v>
+        <v>-1064.5</v>
       </c>
       <c r="C1131" t="n">
         <v>100.7</v>
@@ -24214,7 +24226,7 @@
         <v>45331</v>
       </c>
       <c r="B1136" t="n">
-        <v>-4062.7</v>
+        <v>-4062.8</v>
       </c>
       <c r="C1136" t="n">
         <v>-3001.8</v>
@@ -24234,7 +24246,7 @@
         <v>45332</v>
       </c>
       <c r="B1137" t="n">
-        <v>-10710.3</v>
+        <v>-10710.2</v>
       </c>
       <c r="C1137" t="n">
         <v>-9404.6</v>
@@ -24294,7 +24306,7 @@
         <v>45335</v>
       </c>
       <c r="B1140" t="n">
-        <v>-5420.9</v>
+        <v>-5421</v>
       </c>
       <c r="C1140" t="n">
         <v>-4276.2</v>
@@ -24374,7 +24386,7 @@
         <v>45339</v>
       </c>
       <c r="B1144" t="n">
-        <v>1655.3</v>
+        <v>1655.4</v>
       </c>
       <c r="C1144" t="n">
         <v>2859</v>
@@ -24394,7 +24406,7 @@
         <v>45340</v>
       </c>
       <c r="B1145" t="n">
-        <v>4314.4</v>
+        <v>4314.5</v>
       </c>
       <c r="C1145" t="n">
         <v>5473.9</v>
@@ -24414,7 +24426,7 @@
         <v>45341</v>
       </c>
       <c r="B1146" t="n">
-        <v>-3702.5</v>
+        <v>-3702.6</v>
       </c>
       <c r="C1146" t="n">
         <v>-2621.2</v>
@@ -24434,7 +24446,7 @@
         <v>45342</v>
       </c>
       <c r="B1147" t="n">
-        <v>-5368.1</v>
+        <v>-5368.2</v>
       </c>
       <c r="C1147" t="n">
         <v>-4227.8</v>
@@ -24514,7 +24526,7 @@
         <v>45346</v>
       </c>
       <c r="B1151" t="n">
-        <v>-2124.7</v>
+        <v>-2124.6</v>
       </c>
       <c r="C1151" t="n">
         <v>-703.9</v>
@@ -24694,7 +24706,7 @@
         <v>45355</v>
       </c>
       <c r="B1160" t="n">
-        <v>-12598.2</v>
+        <v>-12598.1</v>
       </c>
       <c r="C1160" t="n">
         <v>-11171.5</v>
@@ -24734,7 +24746,7 @@
         <v>45357</v>
       </c>
       <c r="B1162" t="n">
-        <v>-10586.7</v>
+        <v>-10586.6</v>
       </c>
       <c r="C1162" t="n">
         <v>-9248</v>
@@ -24814,7 +24826,7 @@
         <v>45361</v>
       </c>
       <c r="B1166" t="n">
-        <v>-6475.1</v>
+        <v>-6475</v>
       </c>
       <c r="C1166" t="n">
         <v>-5127.6</v>
@@ -24994,7 +25006,7 @@
         <v>45370</v>
       </c>
       <c r="B1175" t="n">
-        <v>-1490.7</v>
+        <v>-1490.6</v>
       </c>
       <c r="C1175" t="n">
         <v>-574.3</v>
@@ -25014,7 +25026,7 @@
         <v>45371</v>
       </c>
       <c r="B1176" t="n">
-        <v>1522.4</v>
+        <v>1522.3</v>
       </c>
       <c r="C1176" t="n">
         <v>1915.9</v>
@@ -25134,7 +25146,7 @@
         <v>45377</v>
       </c>
       <c r="B1182" t="n">
-        <v>-7462.2</v>
+        <v>-7462.1</v>
       </c>
       <c r="C1182" t="n">
         <v>-7020.6</v>
@@ -25314,7 +25326,7 @@
         <v>45386</v>
       </c>
       <c r="B1191" t="n">
-        <v>-8407.6</v>
+        <v>-8407.700000000001</v>
       </c>
       <c r="C1191" t="n">
         <v>-7798.9</v>
@@ -25394,7 +25406,7 @@
         <v>45390</v>
       </c>
       <c r="B1195" t="n">
-        <v>-2727</v>
+        <v>-2727.1</v>
       </c>
       <c r="C1195" t="n">
         <v>-2595.5</v>
@@ -25454,7 +25466,7 @@
         <v>45393</v>
       </c>
       <c r="B1198" t="n">
-        <v>159.2</v>
+        <v>159.1</v>
       </c>
       <c r="C1198" t="n">
         <v>448.4</v>
@@ -25474,7 +25486,7 @@
         <v>45394</v>
       </c>
       <c r="B1199" t="n">
-        <v>-4404.4</v>
+        <v>-4404.3</v>
       </c>
       <c r="C1199" t="n">
         <v>-4083</v>
@@ -25514,7 +25526,7 @@
         <v>45396</v>
       </c>
       <c r="B1201" t="n">
-        <v>-10668</v>
+        <v>-10668.1</v>
       </c>
       <c r="C1201" t="n">
         <v>-10383.6</v>
@@ -25554,7 +25566,7 @@
         <v>45398</v>
       </c>
       <c r="B1203" t="n">
-        <v>-17478.3</v>
+        <v>-17478.4</v>
       </c>
       <c r="C1203" t="n">
         <v>-17225.6</v>
@@ -25654,7 +25666,7 @@
         <v>45403</v>
       </c>
       <c r="B1208" t="n">
-        <v>-9672.9</v>
+        <v>-9673</v>
       </c>
       <c r="C1208" t="n">
         <v>-9280.9</v>
@@ -25674,7 +25686,7 @@
         <v>45404</v>
       </c>
       <c r="B1209" t="n">
-        <v>-14898.7</v>
+        <v>-14898.6</v>
       </c>
       <c r="C1209" t="n">
         <v>-14545.2</v>
@@ -25834,7 +25846,7 @@
         <v>45412</v>
       </c>
       <c r="B1217" t="n">
-        <v>1177.4</v>
+        <v>1177.3</v>
       </c>
       <c r="C1217" t="n">
         <v>1624.5</v>
@@ -25934,7 +25946,7 @@
         <v>45417</v>
       </c>
       <c r="B1222" t="n">
-        <v>-4547.6</v>
+        <v>-4547.5</v>
       </c>
       <c r="C1222" t="n">
         <v>-4204.2</v>
@@ -25994,7 +26006,7 @@
         <v>45420</v>
       </c>
       <c r="B1225" t="n">
-        <v>-15776.6</v>
+        <v>-15776.7</v>
       </c>
       <c r="C1225" t="n">
         <v>-15485.5</v>
@@ -26054,7 +26066,7 @@
         <v>45423</v>
       </c>
       <c r="B1228" t="n">
-        <v>-13933.7</v>
+        <v>-13933.8</v>
       </c>
       <c r="C1228" t="n">
         <v>-13652.1</v>
@@ -26254,7 +26266,7 @@
         <v>45433</v>
       </c>
       <c r="B1238" t="n">
-        <v>-5810.8</v>
+        <v>-5810.9</v>
       </c>
       <c r="C1238" t="n">
         <v>-5721</v>
@@ -26394,7 +26406,7 @@
         <v>45440</v>
       </c>
       <c r="B1245" t="n">
-        <v>-13759.7</v>
+        <v>-13759.8</v>
       </c>
       <c r="C1245" t="n">
         <v>-13661.4</v>
@@ -26454,7 +26466,7 @@
         <v>45443</v>
       </c>
       <c r="B1248" t="n">
-        <v>-17922</v>
+        <v>-17921.9</v>
       </c>
       <c r="C1248" t="n">
         <v>-17869.2</v>
@@ -26494,7 +26506,7 @@
         <v>45445</v>
       </c>
       <c r="B1250" t="n">
-        <v>-16898.4</v>
+        <v>-16898.5</v>
       </c>
       <c r="C1250" t="n">
         <v>-16669.4</v>
@@ -26594,7 +26606,7 @@
         <v>45450</v>
       </c>
       <c r="B1255" t="n">
-        <v>-18319.6</v>
+        <v>-18319.7</v>
       </c>
       <c r="C1255" t="n">
         <v>-18158.7</v>
@@ -26614,7 +26626,7 @@
         <v>45451</v>
       </c>
       <c r="B1256" t="n">
-        <v>-18188.9</v>
+        <v>-18188.8</v>
       </c>
       <c r="C1256" t="n">
         <v>-17908.1</v>
@@ -26674,7 +26686,7 @@
         <v>45454</v>
       </c>
       <c r="B1259" t="n">
-        <v>-10892.3</v>
+        <v>-10892.2</v>
       </c>
       <c r="C1259" t="n">
         <v>-10661.5</v>
@@ -26734,7 +26746,7 @@
         <v>45457</v>
       </c>
       <c r="B1262" t="n">
-        <v>-4243.4</v>
+        <v>-4243.3</v>
       </c>
       <c r="C1262" t="n">
         <v>-3922.3</v>
@@ -26774,7 +26786,7 @@
         <v>45459</v>
       </c>
       <c r="B1264" t="n">
-        <v>-4475.4</v>
+        <v>-4475.3</v>
       </c>
       <c r="C1264" t="n">
         <v>-4053</v>
@@ -26874,7 +26886,7 @@
         <v>45464</v>
       </c>
       <c r="B1269" t="n">
-        <v>3085.8</v>
+        <v>3085.9</v>
       </c>
       <c r="C1269" t="n">
         <v>3439.2</v>
@@ -26974,7 +26986,7 @@
         <v>45469</v>
       </c>
       <c r="B1274" t="n">
-        <v>-2766.7</v>
+        <v>-2766.6</v>
       </c>
       <c r="C1274" t="n">
         <v>-2284.6</v>
@@ -27094,7 +27106,7 @@
         <v>45475</v>
       </c>
       <c r="B1280" t="n">
-        <v>-7530.5</v>
+        <v>-7530.6</v>
       </c>
       <c r="C1280" t="n">
         <v>-6962.8</v>
@@ -27154,7 +27166,7 @@
         <v>45478</v>
       </c>
       <c r="B1283" t="n">
-        <v>-6661.6</v>
+        <v>-6661.5</v>
       </c>
       <c r="C1283" t="n">
         <v>-6122.7</v>
@@ -27174,7 +27186,7 @@
         <v>45479</v>
       </c>
       <c r="B1284" t="n">
-        <v>-5454.7</v>
+        <v>-5454.6</v>
       </c>
       <c r="C1284" t="n">
         <v>-4776.8</v>
@@ -27194,7 +27206,7 @@
         <v>45480</v>
       </c>
       <c r="B1285" t="n">
-        <v>-5504.7</v>
+        <v>-5504.8</v>
       </c>
       <c r="C1285" t="n">
         <v>-5108</v>
@@ -27334,7 +27346,7 @@
         <v>45487</v>
       </c>
       <c r="B1292" t="n">
-        <v>-4463.9</v>
+        <v>-4463.8</v>
       </c>
       <c r="C1292" t="n">
         <v>-3845.2</v>
@@ -27374,7 +27386,7 @@
         <v>45489</v>
       </c>
       <c r="B1294" t="n">
-        <v>-8288.6</v>
+        <v>-8288.700000000001</v>
       </c>
       <c r="C1294" t="n">
         <v>-7747.3</v>
@@ -27454,7 +27466,7 @@
         <v>45493</v>
       </c>
       <c r="B1298" t="n">
-        <v>-17776.7</v>
+        <v>-17776.6</v>
       </c>
       <c r="C1298" t="n">
         <v>-16999.6</v>
@@ -27554,7 +27566,7 @@
         <v>45498</v>
       </c>
       <c r="B1303" t="n">
-        <v>-18219.9</v>
+        <v>-18220</v>
       </c>
       <c r="C1303" t="n">
         <v>-17517</v>
@@ -28434,7 +28446,7 @@
         <v>45542</v>
       </c>
       <c r="B1347" t="n">
-        <v>-17932.2</v>
+        <v>-17932.1</v>
       </c>
       <c r="C1347" t="n">
         <v>-16879.5</v>
@@ -28474,7 +28486,7 @@
         <v>45544</v>
       </c>
       <c r="B1349" t="n">
-        <v>-10424.1</v>
+        <v>-10424.2</v>
       </c>
       <c r="C1349" t="n">
         <v>-9313.5</v>
@@ -28914,7 +28926,7 @@
         <v>45566</v>
       </c>
       <c r="B1371" t="n">
-        <v>-12153.1</v>
+        <v>-12153.2</v>
       </c>
       <c r="C1371" t="n">
         <v>-11501.6</v>
@@ -29034,7 +29046,7 @@
         <v>45572</v>
       </c>
       <c r="B1377" t="n">
-        <v>-18714</v>
+        <v>-18714.1</v>
       </c>
       <c r="C1377" t="n">
         <v>-18335.2</v>
@@ -29134,7 +29146,7 @@
         <v>45577</v>
       </c>
       <c r="B1382" t="n">
-        <v>-15428.4</v>
+        <v>-15428.5</v>
       </c>
       <c r="C1382" t="n">
         <v>-15285.7</v>
@@ -29294,7 +29306,7 @@
         <v>45585</v>
       </c>
       <c r="B1390" t="n">
-        <v>-2650.3</v>
+        <v>-2650.2</v>
       </c>
       <c r="C1390" t="n">
         <v>-2315.7</v>
@@ -29474,7 +29486,7 @@
         <v>45594</v>
       </c>
       <c r="B1399" t="n">
-        <v>-9275.799999999999</v>
+        <v>-9275.9</v>
       </c>
       <c r="C1399" t="n">
         <v>-8934</v>
@@ -29614,7 +29626,7 @@
         <v>45601</v>
       </c>
       <c r="B1406" t="n">
-        <v>-12575.1</v>
+        <v>-12575</v>
       </c>
       <c r="C1406" t="n">
         <v>-12225.8</v>
@@ -29634,7 +29646,7 @@
         <v>45602</v>
       </c>
       <c r="B1407" t="n">
-        <v>-5497</v>
+        <v>-5497.1</v>
       </c>
       <c r="C1407" t="n">
         <v>-5145.6</v>
@@ -29734,7 +29746,7 @@
         <v>45607</v>
       </c>
       <c r="B1412" t="n">
-        <v>2376.4</v>
+        <v>2376.5</v>
       </c>
       <c r="C1412" t="n">
         <v>2455.1</v>
@@ -29794,7 +29806,7 @@
         <v>45610</v>
       </c>
       <c r="B1415" t="n">
-        <v>-9524.6</v>
+        <v>-9524.700000000001</v>
       </c>
       <c r="C1415" t="n">
         <v>-8535.5</v>
@@ -29894,7 +29906,7 @@
         <v>45615</v>
       </c>
       <c r="B1420" t="n">
-        <v>-11980.5</v>
+        <v>-11980.6</v>
       </c>
       <c r="C1420" t="n">
         <v>-11104.6</v>
@@ -30054,7 +30066,7 @@
         <v>45623</v>
       </c>
       <c r="B1428" t="n">
-        <v>-2300.6</v>
+        <v>-2300.5</v>
       </c>
       <c r="C1428" t="n">
         <v>-1280.2</v>
@@ -30074,7 +30086,7 @@
         <v>45624</v>
       </c>
       <c r="B1429" t="n">
-        <v>-2641.1</v>
+        <v>-2641.2</v>
       </c>
       <c r="C1429" t="n">
         <v>-1329.5</v>
@@ -30194,7 +30206,7 @@
         <v>45630</v>
       </c>
       <c r="B1435" t="n">
-        <v>1949.5</v>
+        <v>1949.4</v>
       </c>
       <c r="C1435" t="n">
         <v>2417</v>
@@ -30374,7 +30386,7 @@
         <v>45639</v>
       </c>
       <c r="B1444" t="n">
-        <v>300.4</v>
+        <v>300.3</v>
       </c>
       <c r="C1444" t="n">
         <v>660.5</v>
@@ -30514,7 +30526,7 @@
         <v>45646</v>
       </c>
       <c r="B1451" t="n">
-        <v>1124.7</v>
+        <v>1124.8</v>
       </c>
       <c r="C1451" t="n">
         <v>2545.6</v>
@@ -30694,7 +30706,7 @@
         <v>45655</v>
       </c>
       <c r="B1460" t="n">
-        <v>4367.6</v>
+        <v>4367.5</v>
       </c>
       <c r="C1460" t="n">
         <v>5824.2</v>
@@ -30794,7 +30806,7 @@
         <v>45660</v>
       </c>
       <c r="B1465" t="n">
-        <v>-1531.5</v>
+        <v>-1531.6</v>
       </c>
       <c r="C1465" t="n">
         <v>-80.59999999999999</v>
@@ -30814,7 +30826,7 @@
         <v>45661</v>
       </c>
       <c r="B1466" t="n">
-        <v>-5088.1</v>
+        <v>-5088</v>
       </c>
       <c r="C1466" t="n">
         <v>-3715.6</v>
@@ -30934,7 +30946,7 @@
         <v>45667</v>
       </c>
       <c r="B1472" t="n">
-        <v>-2503.1</v>
+        <v>-2503</v>
       </c>
       <c r="C1472" t="n">
         <v>-1396.4</v>
@@ -30994,7 +31006,7 @@
         <v>45670</v>
       </c>
       <c r="B1475" t="n">
-        <v>4637.1</v>
+        <v>4637</v>
       </c>
       <c r="C1475" t="n">
         <v>5592.2</v>
@@ -31014,7 +31026,7 @@
         <v>45671</v>
       </c>
       <c r="B1476" t="n">
-        <v>3133.7</v>
+        <v>3133.6</v>
       </c>
       <c r="C1476" t="n">
         <v>4208.5</v>
@@ -31034,7 +31046,7 @@
         <v>45672</v>
       </c>
       <c r="B1477" t="n">
-        <v>809</v>
+        <v>808.9</v>
       </c>
       <c r="C1477" t="n">
         <v>1898.6</v>
@@ -31074,7 +31086,7 @@
         <v>45674</v>
       </c>
       <c r="B1479" t="n">
-        <v>-1434.7</v>
+        <v>-1434.8</v>
       </c>
       <c r="C1479" t="n">
         <v>-744.8</v>
@@ -31134,7 +31146,7 @@
         <v>45677</v>
       </c>
       <c r="B1482" t="n">
-        <v>-2376.9</v>
+        <v>-2376.8</v>
       </c>
       <c r="C1482" t="n">
         <v>-1792.8</v>
@@ -31154,7 +31166,7 @@
         <v>45678</v>
       </c>
       <c r="B1483" t="n">
-        <v>-3090.1</v>
+        <v>-3090.2</v>
       </c>
       <c r="C1483" t="n">
         <v>-1965.4</v>
@@ -31174,7 +31186,7 @@
         <v>45679</v>
       </c>
       <c r="B1484" t="n">
-        <v>-3513.3</v>
+        <v>-3513.2</v>
       </c>
       <c r="C1484" t="n">
         <v>-2452.2</v>
@@ -31334,7 +31346,7 @@
         <v>45687</v>
       </c>
       <c r="B1492" t="n">
-        <v>-1689.7</v>
+        <v>-1689.8</v>
       </c>
       <c r="C1492" t="n">
         <v>-756</v>
@@ -31374,7 +31386,7 @@
         <v>45689</v>
       </c>
       <c r="B1494" t="n">
-        <v>-6878.7</v>
+        <v>-6878.8</v>
       </c>
       <c r="C1494" t="n">
         <v>-5780.4</v>
@@ -31434,7 +31446,7 @@
         <v>45692</v>
       </c>
       <c r="B1497" t="n">
-        <v>-9892.200000000001</v>
+        <v>-9892.299999999999</v>
       </c>
       <c r="C1497" t="n">
         <v>-8960.799999999999</v>
@@ -31454,7 +31466,7 @@
         <v>45693</v>
       </c>
       <c r="B1498" t="n">
-        <v>-8381.200000000001</v>
+        <v>-8381.1</v>
       </c>
       <c r="C1498" t="n">
         <v>-7440.1</v>
@@ -31554,7 +31566,7 @@
         <v>45698</v>
       </c>
       <c r="B1503" t="n">
-        <v>-7905.5</v>
+        <v>-7905.4</v>
       </c>
       <c r="C1503" t="n">
         <v>-6728.6</v>
@@ -31574,7 +31586,7 @@
         <v>45699</v>
       </c>
       <c r="B1504" t="n">
-        <v>-8521.4</v>
+        <v>-8521.5</v>
       </c>
       <c r="C1504" t="n">
         <v>-7363.9</v>
@@ -31794,7 +31806,7 @@
         <v>45710</v>
       </c>
       <c r="B1515" t="n">
-        <v>-7436.7</v>
+        <v>-7436.6</v>
       </c>
       <c r="C1515" t="n">
         <v>-7009.8</v>
@@ -31834,7 +31846,7 @@
         <v>45712</v>
       </c>
       <c r="B1517" t="n">
-        <v>-10646.5</v>
+        <v>-10646.6</v>
       </c>
       <c r="C1517" t="n">
         <v>-9539.9</v>
@@ -31974,7 +31986,7 @@
         <v>45719</v>
       </c>
       <c r="B1524" t="n">
-        <v>-8468.4</v>
+        <v>-8468.5</v>
       </c>
       <c r="C1524" t="n">
         <v>-7912.1</v>
@@ -32034,7 +32046,7 @@
         <v>45722</v>
       </c>
       <c r="B1527" t="n">
-        <v>-3664.2</v>
+        <v>-3664.1</v>
       </c>
       <c r="C1527" t="n">
         <v>-3205.4</v>
@@ -32074,7 +32086,7 @@
         <v>45724</v>
       </c>
       <c r="B1529" t="n">
-        <v>-8718.5</v>
+        <v>-8718.4</v>
       </c>
       <c r="C1529" t="n">
         <v>-8296.1</v>
@@ -32194,7 +32206,7 @@
         <v>45730</v>
       </c>
       <c r="B1535" t="n">
-        <v>-2859.4</v>
+        <v>-2859.5</v>
       </c>
       <c r="C1535" t="n">
         <v>-1935.4</v>
@@ -32254,7 +32266,7 @@
         <v>45733</v>
       </c>
       <c r="B1538" t="n">
-        <v>-909.2</v>
+        <v>-909.3</v>
       </c>
       <c r="C1538" t="n">
         <v>-273.7</v>
@@ -32314,7 +32326,7 @@
         <v>45736</v>
       </c>
       <c r="B1541" t="n">
-        <v>-8804.5</v>
+        <v>-8804.4</v>
       </c>
       <c r="C1541" t="n">
         <v>-7873.6</v>
@@ -32334,7 +32346,7 @@
         <v>45737</v>
       </c>
       <c r="B1542" t="n">
-        <v>-14163.5</v>
+        <v>-14163.4</v>
       </c>
       <c r="C1542" t="n">
         <v>-13049.4</v>
@@ -32354,7 +32366,7 @@
         <v>45738</v>
       </c>
       <c r="B1543" t="n">
-        <v>-5752.1</v>
+        <v>-5752</v>
       </c>
       <c r="C1543" t="n">
         <v>-4730.6</v>
@@ -32374,7 +32386,7 @@
         <v>45739</v>
       </c>
       <c r="B1544" t="n">
-        <v>-1939.3</v>
+        <v>-1939.4</v>
       </c>
       <c r="C1544" t="n">
         <v>-910.7</v>
@@ -32434,7 +32446,7 @@
         <v>45742</v>
       </c>
       <c r="B1547" t="n">
-        <v>-3012.2</v>
+        <v>-3012.3</v>
       </c>
       <c r="C1547" t="n">
         <v>-2518.6</v>
@@ -32454,7 +32466,7 @@
         <v>45743</v>
       </c>
       <c r="B1548" t="n">
-        <v>-5417.1</v>
+        <v>-5417</v>
       </c>
       <c r="C1548" t="n">
         <v>-4991.5</v>
@@ -32574,7 +32586,7 @@
         <v>45749</v>
       </c>
       <c r="B1554" t="n">
-        <v>-8119</v>
+        <v>-8118.9</v>
       </c>
       <c r="C1554" t="n">
         <v>-7674</v>
@@ -32634,7 +32646,7 @@
         <v>45752</v>
       </c>
       <c r="B1557" t="n">
-        <v>-13663.3</v>
+        <v>-13663.4</v>
       </c>
       <c r="C1557" t="n">
         <v>-13305</v>
@@ -32714,7 +32726,7 @@
         <v>45756</v>
       </c>
       <c r="B1561" t="n">
-        <v>-13396.4</v>
+        <v>-13396.3</v>
       </c>
       <c r="C1561" t="n">
         <v>-12905.1</v>
@@ -32774,7 +32786,7 @@
         <v>45759</v>
       </c>
       <c r="B1564" t="n">
-        <v>-14773.3</v>
+        <v>-14773.4</v>
       </c>
       <c r="C1564" t="n">
         <v>-14514.6</v>
@@ -32794,7 +32806,7 @@
         <v>45760</v>
       </c>
       <c r="B1565" t="n">
-        <v>-7903.5</v>
+        <v>-7903.4</v>
       </c>
       <c r="C1565" t="n">
         <v>-7591.5</v>
@@ -32814,7 +32826,7 @@
         <v>45761</v>
       </c>
       <c r="B1566" t="n">
-        <v>-6696</v>
+        <v>-6696.1</v>
       </c>
       <c r="C1566" t="n">
         <v>-6558</v>
@@ -32834,7 +32846,7 @@
         <v>45762</v>
       </c>
       <c r="B1567" t="n">
-        <v>-15208.3</v>
+        <v>-15208.2</v>
       </c>
       <c r="C1567" t="n">
         <v>-14264.6</v>
@@ -32874,7 +32886,7 @@
         <v>45764</v>
       </c>
       <c r="B1569" t="n">
-        <v>-7248.3</v>
+        <v>-7248.4</v>
       </c>
       <c r="C1569" t="n">
         <v>-6893.9</v>
@@ -32934,7 +32946,7 @@
         <v>45767</v>
       </c>
       <c r="B1572" t="n">
-        <v>-365.7</v>
+        <v>-365.6</v>
       </c>
       <c r="C1572" t="n">
         <v>-36.9</v>
@@ -33174,7 +33186,7 @@
         <v>45779</v>
       </c>
       <c r="B1584" t="n">
-        <v>-14583.2</v>
+        <v>-14583.1</v>
       </c>
       <c r="C1584" t="n">
         <v>-14403.7</v>
@@ -33274,7 +33286,7 @@
         <v>45784</v>
       </c>
       <c r="B1589" t="n">
-        <v>-18204</v>
+        <v>-18203.9</v>
       </c>
       <c r="C1589" t="n">
         <v>-18083.7</v>
@@ -33314,7 +33326,7 @@
         <v>45786</v>
       </c>
       <c r="B1591" t="n">
-        <v>-19322.1</v>
+        <v>-19322</v>
       </c>
       <c r="C1591" t="n">
         <v>-19024.8</v>
@@ -33334,7 +33346,7 @@
         <v>45787</v>
       </c>
       <c r="B1592" t="n">
-        <v>-19345.9</v>
+        <v>-19345.8</v>
       </c>
       <c r="C1592" t="n">
         <v>-19021.8</v>
@@ -33354,7 +33366,7 @@
         <v>45788</v>
       </c>
       <c r="B1593" t="n">
-        <v>-15350.2</v>
+        <v>-15350.1</v>
       </c>
       <c r="C1593" t="n">
         <v>-14953.2</v>
@@ -33374,7 +33386,7 @@
         <v>45789</v>
       </c>
       <c r="B1594" t="n">
-        <v>-18481.6</v>
+        <v>-18481.7</v>
       </c>
       <c r="C1594" t="n">
         <v>-18305.4</v>
@@ -33414,7 +33426,7 @@
         <v>45791</v>
       </c>
       <c r="B1596" t="n">
-        <v>-8271.6</v>
+        <v>-8271.5</v>
       </c>
       <c r="C1596" t="n">
         <v>-7943.8</v>
@@ -33594,7 +33606,7 @@
         <v>45800</v>
       </c>
       <c r="B1605" t="n">
-        <v>-12263.6</v>
+        <v>-12263.7</v>
       </c>
       <c r="C1605" t="n">
         <v>-12111.8</v>
@@ -33654,7 +33666,7 @@
         <v>45803</v>
       </c>
       <c r="B1608" t="n">
-        <v>-18495.3</v>
+        <v>-18495.2</v>
       </c>
       <c r="C1608" t="n">
         <v>-18290.2</v>
@@ -33794,7 +33806,7 @@
         <v>45810</v>
       </c>
       <c r="B1615" t="n">
-        <v>-18256.9</v>
+        <v>-18256.8</v>
       </c>
       <c r="C1615" t="n">
         <v>-17999.9</v>
@@ -33814,7 +33826,7 @@
         <v>45811</v>
       </c>
       <c r="B1616" t="n">
-        <v>-8473.700000000001</v>
+        <v>-8473.6</v>
       </c>
       <c r="C1616" t="n">
         <v>-8266.5</v>
@@ -33894,7 +33906,7 @@
         <v>45815</v>
       </c>
       <c r="B1620" t="n">
-        <v>-222</v>
+        <v>-222.1</v>
       </c>
       <c r="C1620" t="n">
         <v>116.6</v>
@@ -33914,7 +33926,7 @@
         <v>45816</v>
       </c>
       <c r="B1621" t="n">
-        <v>-16739.4</v>
+        <v>-16739.5</v>
       </c>
       <c r="C1621" t="n">
         <v>-16429</v>
@@ -33954,7 +33966,7 @@
         <v>45818</v>
       </c>
       <c r="B1623" t="n">
-        <v>-17632.6</v>
+        <v>-17632.7</v>
       </c>
       <c r="C1623" t="n">
         <v>-17421.5</v>
@@ -33974,7 +33986,7 @@
         <v>45819</v>
       </c>
       <c r="B1624" t="n">
-        <v>-16104.2</v>
+        <v>-16104.1</v>
       </c>
       <c r="C1624" t="n">
         <v>-15707.5</v>
@@ -34014,7 +34026,7 @@
         <v>45821</v>
       </c>
       <c r="B1626" t="n">
-        <v>-14853.1</v>
+        <v>-14853</v>
       </c>
       <c r="C1626" t="n">
         <v>-14454.7</v>
@@ -34114,7 +34126,7 @@
         <v>45826</v>
       </c>
       <c r="B1631" t="n">
-        <v>-15442.3</v>
+        <v>-15442.2</v>
       </c>
       <c r="C1631" t="n">
         <v>-14777.6</v>
@@ -34254,7 +34266,7 @@
         <v>45833</v>
       </c>
       <c r="B1638" t="n">
-        <v>-10061.8</v>
+        <v>-10061.7</v>
       </c>
       <c r="C1638" t="n">
         <v>-9661.200000000001</v>
@@ -34394,7 +34406,7 @@
         <v>45840</v>
       </c>
       <c r="B1645" t="n">
-        <v>-12833</v>
+        <v>-12833.1</v>
       </c>
       <c r="C1645" t="n">
         <v>-12149.6</v>
@@ -34574,7 +34586,7 @@
         <v>45849</v>
       </c>
       <c r="B1654" t="n">
-        <v>-8041.6</v>
+        <v>-8041.7</v>
       </c>
       <c r="C1654" t="n">
         <v>-7397.4</v>
@@ -34614,7 +34626,7 @@
         <v>45851</v>
       </c>
       <c r="B1656" t="n">
-        <v>-2897.5</v>
+        <v>-2897.4</v>
       </c>
       <c r="C1656" t="n">
         <v>-2360.2</v>
@@ -34714,7 +34726,7 @@
         <v>45856</v>
       </c>
       <c r="B1661" t="n">
-        <v>-15850.4</v>
+        <v>-15850.3</v>
       </c>
       <c r="C1661" t="n">
         <v>-15220.2</v>
@@ -34834,7 +34846,7 @@
         <v>45862</v>
       </c>
       <c r="B1667" t="n">
-        <v>-12655</v>
+        <v>-12655.1</v>
       </c>
       <c r="C1667" t="n">
         <v>-12020.2</v>
@@ -34994,7 +35006,7 @@
         <v>45870</v>
       </c>
       <c r="B1675" t="n">
-        <v>-18471.1</v>
+        <v>-18471.2</v>
       </c>
       <c r="C1675" t="n">
         <v>-17860</v>
@@ -35054,7 +35066,7 @@
         <v>45873</v>
       </c>
       <c r="B1678" t="n">
-        <v>-11729.3</v>
+        <v>-11729.4</v>
       </c>
       <c r="C1678" t="n">
         <v>-11053.2</v>
@@ -35214,7 +35226,7 @@
         <v>45881</v>
       </c>
       <c r="B1686" t="n">
-        <v>-17969.9</v>
+        <v>-17970</v>
       </c>
       <c r="C1686" t="n">
         <v>-17170.1</v>
@@ -35274,7 +35286,7 @@
         <v>45884</v>
       </c>
       <c r="B1689" t="n">
-        <v>-17890.1</v>
+        <v>-17890.2</v>
       </c>
       <c r="C1689" t="n">
         <v>-17197.1</v>
@@ -35354,7 +35366,7 @@
         <v>45888</v>
       </c>
       <c r="B1693" t="n">
-        <v>-15873.1</v>
+        <v>-15873</v>
       </c>
       <c r="C1693" t="n">
         <v>-15179.6</v>
@@ -35474,7 +35486,7 @@
         <v>45894</v>
       </c>
       <c r="B1699" t="n">
-        <v>-10030.8</v>
+        <v>-10030.9</v>
       </c>
       <c r="C1699" t="n">
         <v>-9499.700000000001</v>
@@ -35494,7 +35506,7 @@
         <v>45895</v>
       </c>
       <c r="B1700" t="n">
-        <v>-17270.6</v>
+        <v>-17270.7</v>
       </c>
       <c r="C1700" t="n">
         <v>-16691</v>
@@ -35594,7 +35606,7 @@
         <v>45900</v>
       </c>
       <c r="B1705" t="n">
-        <v>-7749.2</v>
+        <v>-7749.3</v>
       </c>
       <c r="C1705" t="n">
         <v>-7389.6</v>
@@ -35614,7 +35626,7 @@
         <v>45901</v>
       </c>
       <c r="B1706" t="n">
-        <v>-9573.799999999999</v>
+        <v>-9573.9</v>
       </c>
       <c r="C1706" t="n">
         <v>-9136.200000000001</v>
@@ -35674,7 +35686,7 @@
         <v>45904</v>
       </c>
       <c r="B1709" t="n">
-        <v>-11844.5</v>
+        <v>-11844.4</v>
       </c>
       <c r="C1709" t="n">
         <v>-11056.8</v>
@@ -35814,7 +35826,7 @@
         <v>45911</v>
       </c>
       <c r="B1716" t="n">
-        <v>-16270.6</v>
+        <v>-16270.5</v>
       </c>
       <c r="C1716" t="n">
         <v>-15844.2</v>
@@ -35834,7 +35846,7 @@
         <v>45912</v>
       </c>
       <c r="B1717" t="n">
-        <v>-18615.5</v>
+        <v>-18615.4</v>
       </c>
       <c r="C1717" t="n">
         <v>-18209.4</v>
@@ -35914,7 +35926,7 @@
         <v>45916</v>
       </c>
       <c r="B1721" t="n">
-        <v>-19711.1</v>
+        <v>-19711.2</v>
       </c>
       <c r="C1721" t="n">
         <v>-19129.2</v>
@@ -35934,7 +35946,7 @@
         <v>45917</v>
       </c>
       <c r="B1722" t="n">
-        <v>-9972</v>
+        <v>-9971.9</v>
       </c>
       <c r="C1722" t="n">
         <v>-9412.799999999999</v>
@@ -35994,7 +36006,7 @@
         <v>45920</v>
       </c>
       <c r="B1725" t="n">
-        <v>-10140</v>
+        <v>-10139.9</v>
       </c>
       <c r="C1725" t="n">
         <v>-9435.299999999999</v>
@@ -36014,7 +36026,7 @@
         <v>45921</v>
       </c>
       <c r="B1726" t="n">
-        <v>-9803.200000000001</v>
+        <v>-9803.299999999999</v>
       </c>
       <c r="C1726" t="n">
         <v>-9185</v>
@@ -36114,7 +36126,7 @@
         <v>45926</v>
       </c>
       <c r="B1731" t="n">
-        <v>-9604.4</v>
+        <v>-9604.5</v>
       </c>
       <c r="C1731" t="n">
         <v>-9171.4</v>
@@ -36134,7 +36146,7 @@
         <v>45927</v>
       </c>
       <c r="B1732" t="n">
-        <v>-9455.5</v>
+        <v>-9455.6</v>
       </c>
       <c r="C1732" t="n">
         <v>-8734</v>
@@ -36154,7 +36166,7 @@
         <v>45928</v>
       </c>
       <c r="B1733" t="n">
-        <v>-75.7</v>
+        <v>-75.59999999999999</v>
       </c>
       <c r="C1733" t="n">
         <v>721.7</v>
@@ -36194,7 +36206,7 @@
         <v>45930</v>
       </c>
       <c r="B1735" t="n">
-        <v>-11659.5</v>
+        <v>-11659.6</v>
       </c>
       <c r="C1735" t="n">
         <v>-11096.4</v>
@@ -36234,7 +36246,7 @@
         <v>45932</v>
       </c>
       <c r="B1737" t="n">
-        <v>-13239.8</v>
+        <v>-13239.7</v>
       </c>
       <c r="C1737" t="n">
         <v>-12901</v>
@@ -36494,7 +36506,7 @@
         <v>45945</v>
       </c>
       <c r="B1750" t="n">
-        <v>-15828.5</v>
+        <v>-15828.4</v>
       </c>
       <c r="C1750" t="n">
         <v>-15646.8</v>
@@ -36514,7 +36526,7 @@
         <v>45946</v>
       </c>
       <c r="B1751" t="n">
-        <v>-14130.4</v>
+        <v>-14130.5</v>
       </c>
       <c r="C1751" t="n">
         <v>-13949.1</v>
@@ -36534,7 +36546,7 @@
         <v>45947</v>
       </c>
       <c r="B1752" t="n">
-        <v>-14134.8</v>
+        <v>-14134.7</v>
       </c>
       <c r="C1752" t="n">
         <v>-13954.2</v>
@@ -36554,7 +36566,7 @@
         <v>45948</v>
       </c>
       <c r="B1753" t="n">
-        <v>-13662.9</v>
+        <v>-13662.8</v>
       </c>
       <c r="C1753" t="n">
         <v>-13492</v>
@@ -36574,7 +36586,7 @@
         <v>45949</v>
       </c>
       <c r="B1754" t="n">
-        <v>-10876.3</v>
+        <v>-10876.2</v>
       </c>
       <c r="C1754" t="n">
         <v>-10703.2</v>
@@ -36794,7 +36806,7 @@
         <v>45960</v>
       </c>
       <c r="B1765" t="n">
-        <v>-13077.1</v>
+        <v>-13077</v>
       </c>
       <c r="C1765" t="n">
         <v>-12906.2</v>
@@ -37074,7 +37086,7 @@
         <v>45974</v>
       </c>
       <c r="B1779" t="n">
-        <v>-12664.1</v>
+        <v>-12664</v>
       </c>
       <c r="C1779" t="n">
         <v>-11733.1</v>
@@ -37114,7 +37126,7 @@
         <v>45976</v>
       </c>
       <c r="B1781" t="n">
-        <v>-14903</v>
+        <v>-14903.1</v>
       </c>
       <c r="C1781" t="n">
         <v>-14741.4</v>
@@ -37354,7 +37366,7 @@
         <v>45988</v>
       </c>
       <c r="B1793" t="n">
-        <v>-14067</v>
+        <v>-14066.9</v>
       </c>
       <c r="C1793" t="n">
         <v>-12861.9</v>
@@ -37474,7 +37486,7 @@
         <v>45994</v>
       </c>
       <c r="B1799" t="n">
-        <v>-739.7</v>
+        <v>-739.8</v>
       </c>
       <c r="C1799" t="n">
         <v>-202</v>
@@ -37514,7 +37526,7 @@
         <v>45996</v>
       </c>
       <c r="B1801" t="n">
-        <v>-11879.7</v>
+        <v>-11879.6</v>
       </c>
       <c r="C1801" t="n">
         <v>-11408</v>
@@ -37574,7 +37586,7 @@
         <v>45999</v>
       </c>
       <c r="B1804" t="n">
-        <v>-17082.8</v>
+        <v>-17082.7</v>
       </c>
       <c r="C1804" t="n">
         <v>-16162.8</v>
@@ -37594,7 +37606,7 @@
         <v>46000</v>
       </c>
       <c r="B1805" t="n">
-        <v>-20224.7</v>
+        <v>-20224.8</v>
       </c>
       <c r="C1805" t="n">
         <v>-19094.2</v>
@@ -37614,7 +37626,7 @@
         <v>46001</v>
       </c>
       <c r="B1806" t="n">
-        <v>-16294.4</v>
+        <v>-16294.3</v>
       </c>
       <c r="C1806" t="n">
         <v>-15240.3</v>
@@ -37694,7 +37706,7 @@
         <v>46005</v>
       </c>
       <c r="B1810" t="n">
-        <v>-5858.7</v>
+        <v>-5858.8</v>
       </c>
       <c r="C1810" t="n">
         <v>-5459</v>
@@ -37714,7 +37726,7 @@
         <v>46006</v>
       </c>
       <c r="B1811" t="n">
-        <v>-12961.4</v>
+        <v>-12961.5</v>
       </c>
       <c r="C1811" t="n">
         <v>-11901</v>
@@ -37734,7 +37746,7 @@
         <v>46007</v>
       </c>
       <c r="B1812" t="n">
-        <v>-11310.3</v>
+        <v>-11310.2</v>
       </c>
       <c r="C1812" t="n">
         <v>-10668.2</v>
@@ -37794,7 +37806,7 @@
         <v>46010</v>
       </c>
       <c r="B1815" t="n">
-        <v>-17356.9</v>
+        <v>-17357</v>
       </c>
       <c r="C1815" t="n">
         <v>-16909.8</v>
@@ -37874,7 +37886,7 @@
         <v>46014</v>
       </c>
       <c r="B1819" t="n">
-        <v>-7681.3</v>
+        <v>-7681.2</v>
       </c>
       <c r="C1819" t="n">
         <v>-6440</v>
@@ -37934,7 +37946,7 @@
         <v>46017</v>
       </c>
       <c r="B1822" t="n">
-        <v>-18246.9</v>
+        <v>-18246.8</v>
       </c>
       <c r="C1822" t="n">
         <v>-17139.8</v>
@@ -37954,7 +37966,7 @@
         <v>46018</v>
       </c>
       <c r="B1823" t="n">
-        <v>-16413.5</v>
+        <v>-16413.6</v>
       </c>
       <c r="C1823" t="n">
         <v>-15305.8</v>
@@ -38074,7 +38086,7 @@
         <v>46024</v>
       </c>
       <c r="B1829" t="n">
-        <v>-649.9</v>
+        <v>-649.8</v>
       </c>
       <c r="C1829" t="n">
         <v>613.7</v>
@@ -38094,7 +38106,7 @@
         <v>46025</v>
       </c>
       <c r="B1830" t="n">
-        <v>-8987.700000000001</v>
+        <v>-8987.6</v>
       </c>
       <c r="C1830" t="n">
         <v>-7853.5</v>
@@ -38174,7 +38186,7 @@
         <v>46029</v>
       </c>
       <c r="B1834" t="n">
-        <v>-2632.9</v>
+        <v>-2633</v>
       </c>
       <c r="C1834" t="n">
         <v>-1273.8</v>
@@ -38234,7 +38246,7 @@
         <v>46032</v>
       </c>
       <c r="B1837" t="n">
-        <v>-9784.700000000001</v>
+        <v>-9784.799999999999</v>
       </c>
       <c r="C1837" t="n">
         <v>-8547.6</v>
@@ -38334,7 +38346,7 @@
         <v>46037</v>
       </c>
       <c r="B1842" t="n">
-        <v>-4370.6</v>
+        <v>-4370.5</v>
       </c>
       <c r="C1842" t="n">
         <v>-3087.5</v>
@@ -38514,7 +38526,7 @@
         <v>46046</v>
       </c>
       <c r="B1851" t="n">
-        <v>-5973.8</v>
+        <v>-5973.9</v>
       </c>
       <c r="C1851" t="n">
         <v>-4808.2</v>
@@ -38574,7 +38586,7 @@
         <v>46049</v>
       </c>
       <c r="B1854" t="n">
-        <v>-14402.7</v>
+        <v>-14402.6</v>
       </c>
       <c r="C1854" t="n">
         <v>-13094.1</v>
@@ -38894,7 +38906,7 @@
         <v>46065</v>
       </c>
       <c r="B1870" t="n">
-        <v>-13301.3</v>
+        <v>-13301.4</v>
       </c>
       <c r="C1870" t="n">
         <v>-12319.8</v>
@@ -38994,7 +39006,7 @@
         <v>46070</v>
       </c>
       <c r="B1875" t="n">
-        <v>-18490.2</v>
+        <v>-18490.1</v>
       </c>
       <c r="C1875" t="n">
         <v>-17491.2</v>
@@ -39214,7 +39226,7 @@
         <v>46081</v>
       </c>
       <c r="B1886" t="n">
-        <v>-15675.1</v>
+        <v>-15675.2</v>
       </c>
       <c r="C1886" t="n">
         <v>-14809</v>
@@ -39234,7 +39246,7 @@
         <v>46082</v>
       </c>
       <c r="B1887" t="n">
-        <v>-5558.8</v>
+        <v>-5558.7</v>
       </c>
       <c r="C1887" t="n">
         <v>-4688.9</v>
@@ -39254,7 +39266,7 @@
         <v>46083</v>
       </c>
       <c r="B1888" t="n">
-        <v>-15285.3</v>
+        <v>-15285.2</v>
       </c>
       <c r="C1888" t="n">
         <v>-14597.7</v>
@@ -39274,7 +39286,7 @@
         <v>46084</v>
       </c>
       <c r="B1889" t="n">
-        <v>-14287.7</v>
+        <v>-14287.8</v>
       </c>
       <c r="C1889" t="n">
         <v>-13444.1</v>
@@ -39294,7 +39306,7 @@
         <v>46085</v>
       </c>
       <c r="B1890" t="n">
-        <v>-15377.5</v>
+        <v>-15377.6</v>
       </c>
       <c r="C1890" t="n">
         <v>-14554.1</v>
@@ -39314,7 +39326,7 @@
         <v>46086</v>
       </c>
       <c r="B1891" t="n">
-        <v>-13389.3</v>
+        <v>-13389.2</v>
       </c>
       <c r="C1891" t="n">
         <v>-12431.4</v>
@@ -39374,7 +39386,7 @@
         <v>46089</v>
       </c>
       <c r="B1894" t="n">
-        <v>-3308.5</v>
+        <v>-3308.6</v>
       </c>
       <c r="C1894" t="n">
         <v>-2433.5</v>
@@ -39554,7 +39566,7 @@
         <v>46098</v>
       </c>
       <c r="B1903" t="n">
-        <v>-13256.2</v>
+        <v>-13256.1</v>
       </c>
       <c r="C1903" t="n">
         <v>-12529.5</v>
@@ -39654,7 +39666,7 @@
         <v>46103</v>
       </c>
       <c r="B1908" t="n">
-        <v>1614.8</v>
+        <v>1614.9</v>
       </c>
       <c r="C1908" t="n">
         <v>2371.1</v>
@@ -39734,7 +39746,7 @@
         <v>46107</v>
       </c>
       <c r="B1912" t="n">
-        <v>-13385.4</v>
+        <v>-13385.5</v>
       </c>
       <c r="C1912" t="n">
         <v>-12636.9</v>
@@ -39774,7 +39786,7 @@
         <v>46109</v>
       </c>
       <c r="B1914" t="n">
-        <v>-9052.799999999999</v>
+        <v>-9052.700000000001</v>
       </c>
       <c r="C1914" t="n">
         <v>-8092.2</v>
@@ -39874,7 +39886,7 @@
         <v>46114</v>
       </c>
       <c r="B1919" t="n">
-        <v>-18784.2</v>
+        <v>-18784.1</v>
       </c>
       <c r="C1919" t="n">
         <v>-18385.9</v>
@@ -40894,7 +40906,7 @@
         <v>46165</v>
       </c>
       <c r="B1970" t="n">
-        <v>-19020.2</v>
+        <v>-19020.3</v>
       </c>
       <c r="C1970" t="n">
         <v>-18937.4</v>
@@ -40934,7 +40946,7 @@
         <v>46167</v>
       </c>
       <c r="B1972" t="n">
-        <v>-18042.5</v>
+        <v>-18042.6</v>
       </c>
       <c r="C1972" t="n">
         <v>-17992.2</v>
@@ -41234,7 +41246,7 @@
         <v>46182</v>
       </c>
       <c r="B1987" t="n">
-        <v>-14146.9</v>
+        <v>-14146.8</v>
       </c>
       <c r="C1987" t="n">
         <v>-13910.6</v>
@@ -41254,7 +41266,7 @@
         <v>46183</v>
       </c>
       <c r="B1988" t="n">
-        <v>-14804.9</v>
+        <v>-14804.8</v>
       </c>
       <c r="C1988" t="n">
         <v>-14572</v>
@@ -41294,7 +41306,7 @@
         <v>46185</v>
       </c>
       <c r="B1990" t="n">
-        <v>-18354.9</v>
+        <v>-18354.8</v>
       </c>
       <c r="C1990" t="n">
         <v>-18055</v>
@@ -41414,7 +41426,7 @@
         <v>46191</v>
       </c>
       <c r="B1996" t="n">
-        <v>-14033.2</v>
+        <v>-14033.1</v>
       </c>
       <c r="C1996" t="n">
         <v>-13643.6</v>
@@ -41474,7 +41486,7 @@
         <v>46194</v>
       </c>
       <c r="B1999" t="n">
-        <v>-15695.7</v>
+        <v>-15695.8</v>
       </c>
       <c r="C1999" t="n">
         <v>-15058.7</v>
@@ -41714,7 +41726,7 @@
         <v>46206</v>
       </c>
       <c r="B2011" t="n">
-        <v>-20678.6</v>
+        <v>-20678.5</v>
       </c>
       <c r="C2011" t="n">
         <v>-19998.1</v>
@@ -41794,7 +41806,7 @@
         <v>46210</v>
       </c>
       <c r="B2015" t="n">
-        <v>-18851.5</v>
+        <v>-18851.4</v>
       </c>
       <c r="C2015" t="n">
         <v>-18228.2</v>
@@ -41834,7 +41846,7 @@
         <v>46212</v>
       </c>
       <c r="B2017" t="n">
-        <v>-17982.8</v>
+        <v>-17982.9</v>
       </c>
       <c r="C2017" t="n">
         <v>-17207.9</v>
@@ -41874,7 +41886,7 @@
         <v>46214</v>
       </c>
       <c r="B2019" t="n">
-        <v>-19402.6</v>
+        <v>-19402.7</v>
       </c>
       <c r="C2019" t="n">
         <v>-18652.7</v>
@@ -41954,7 +41966,7 @@
         <v>46218</v>
       </c>
       <c r="B2023" t="n">
-        <v>-15726.1</v>
+        <v>-15726</v>
       </c>
       <c r="C2023" t="n">
         <v>-14777.6</v>
@@ -41974,7 +41986,7 @@
         <v>46219</v>
       </c>
       <c r="B2024" t="n">
-        <v>-17041</v>
+        <v>-17041.1</v>
       </c>
       <c r="C2024" t="n">
         <v>-16122.7</v>
@@ -42234,7 +42246,7 @@
         <v>46232</v>
       </c>
       <c r="B2037" t="n">
-        <v>-18797.4</v>
+        <v>-18797.5</v>
       </c>
       <c r="C2037" t="n">
         <v>-17914</v>
@@ -42274,7 +42286,7 @@
         <v>46234</v>
       </c>
       <c r="B2039" t="n">
-        <v>-22779.6</v>
+        <v>-22779.7</v>
       </c>
       <c r="C2039" t="n">
         <v>-21922.1</v>
@@ -42334,7 +42346,7 @@
         <v>46237</v>
       </c>
       <c r="B2042" t="n">
-        <v>-18809.5</v>
+        <v>-18809.6</v>
       </c>
       <c r="C2042" t="n">
         <v>-17766.9</v>
@@ -42374,7 +42386,7 @@
         <v>46239</v>
       </c>
       <c r="B2044" t="n">
-        <v>-17477.6</v>
+        <v>-17477.7</v>
       </c>
       <c r="C2044" t="n">
         <v>-16269.6</v>
@@ -42434,7 +42446,7 @@
         <v>46242</v>
       </c>
       <c r="B2047" t="n">
-        <v>-18551.2</v>
+        <v>-18551.3</v>
       </c>
       <c r="C2047" t="n">
         <v>-17796.7</v>
@@ -42514,7 +42526,7 @@
         <v>46246</v>
       </c>
       <c r="B2051" t="n">
-        <v>-20922.2</v>
+        <v>-20922.1</v>
       </c>
       <c r="C2051" t="n">
         <v>-20178.9</v>
@@ -42594,7 +42606,7 @@
         <v>46250</v>
       </c>
       <c r="B2055" t="n">
-        <v>-17785.5</v>
+        <v>-17785.6</v>
       </c>
       <c r="C2055" t="n">
         <v>-17088.2</v>
@@ -42714,7 +42726,7 @@
         <v>46256</v>
       </c>
       <c r="B2061" t="n">
-        <v>-19954.3</v>
+        <v>-19954.2</v>
       </c>
       <c r="C2061" t="n">
         <v>-19316.2</v>
@@ -43347,6 +43359,466 @@
       </c>
       <c r="F2092" t="n">
         <v>-63902.2</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B2093" t="n">
+        <v>-17746.7</v>
+      </c>
+      <c r="C2093" t="n">
+        <v>-16857.5</v>
+      </c>
+      <c r="D2093" t="n">
+        <v>-889.2</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>15246.6</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>-59135.9</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>-13343</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>-12444</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>-899.1</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>7934.9</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>-55296.8</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>-15739</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>-14856</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>-882.9</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>5364.3</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>-52636.6</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="4" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>-21469.1</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>-20659.8</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>-809.4</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>-16097.2</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>-55209.3</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>-19186.5</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>-18408.6</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>-777.9</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>18745.9</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>-62290</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="4" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2098" t="n">
+        <v>-16986.9</v>
+      </c>
+      <c r="C2098" t="n">
+        <v>-16111.4</v>
+      </c>
+      <c r="D2098" t="n">
+        <v>-875.4</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>4153.2</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>-44551.7</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>-20774.3</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>-19884.3</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>-890</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>-12071.8</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>-19476.1</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>-16822.7</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>-15948.4</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>-874.4</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>6253</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>-39926.4</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>-13950.8</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>-13292.2</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>-658.6</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>-14122</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>-37886.8</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>-18779.7</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>-17901.6</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>-878</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>-25740.2</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>-36081.8</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>-18188.7</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>-17442.2</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>-746.5</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>14490.3</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>-44307.4</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>-17830.9</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>-17045.8</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>-785.1</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>36792.8</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>-49421.3</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>-18123.2</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>-17148.7</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>-974.6</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>38914.5</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>-27603</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>-17349.1</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>-16171.5</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>-1177.6</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>26192.6</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>-49936.7</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>-19498.7</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>-18341</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>-1157.7</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>12591.5</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>-52626.3</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>-19117.5</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>-18086.8</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>-1030.8</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>-1887.4</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>-45490.9</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>-18653.5</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>-18404.5</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>-249</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>18498.8</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>-47972.2</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>-20349.4</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>-20025.4</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>-324</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>22029.6</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>-65498</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>-18922.8</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>-18605.2</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>-317.7</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>28596.3</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>-61333.3</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>-19501.6</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>-19138.5</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>-363.2</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>16130</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>-73566.2</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>-11274.2</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>-10918.6</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>-355.6</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>32336.9</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>-66000.60000000001</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>-12738</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>-12381.3</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>-356.7</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>25665.6</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>-60530.9</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>-14693.8</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>-14338.1</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>-355.7</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>23361.4</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>-65434.2</v>
       </c>
     </row>
   </sheetData>
